--- a/templates/pi/Proforma_Invoice_template -2.xlsx
+++ b/templates/pi/Proforma_Invoice_template -2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13380"/>
+    <workbookView windowWidth="24750" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="quotation" sheetId="1" r:id="rId1"/>
@@ -924,19 +924,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>321310</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:colOff>39370</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>158750</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>958215</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>11430</xdr:rowOff>
+      <xdr:colOff>711200</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>151765</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="图片 2" descr="香港盖章"/>
+        <xdr:cNvPr id="4" name="图片 3" descr="香港-原图(1)"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -948,9 +948,9 @@
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
-        <a:xfrm rot="21360000">
-          <a:off x="3738245" y="234950"/>
-          <a:ext cx="2754630" cy="1402080"/>
+        <a:xfrm rot="21240000">
+          <a:off x="3835400" y="158750"/>
+          <a:ext cx="3025140" cy="1402715"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1221,17 +1221,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H71"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14.5" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="12.9444444444444" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5277777777778" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12.9416666666667" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.525" style="1" customWidth="1"/>
     <col min="3" max="3" width="11.1666666666667" style="1" customWidth="1"/>
-    <col min="4" max="4" width="7.18518518518519" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.6203703703704" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.37962962962963" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.8796296296296" style="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5092592592593" style="1" customWidth="1"/>
-    <col min="9" max="9" width="12.6388888888889" style="1" customWidth="1"/>
+    <col min="4" max="4" width="7.18333333333333" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6166666666667" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.38333333333333" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.8833333333333" style="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5083333333333" style="1" customWidth="1"/>
+    <col min="9" max="9" width="12.6416666666667" style="1" customWidth="1"/>
     <col min="10" max="16384" width="8.66666666666667" style="1"/>
   </cols>
   <sheetData>
